--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catalog" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,163 +351,1539 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G66"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>stock_status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
+      <c r="A1" t="str">
+        <v>sku</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>price</v>
+      </c>
+      <c r="F1" t="str">
+        <v>stock_status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>metadata</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AGENT-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bruce - O Assistente Cognitivo Corporativo</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Uma inteligência artificial desenhada para automatizar tarefas complexas, analisar dados financeiros e interagir com clientes em tempo real. Bruce aprende com o contexto da sua empresa e se adapta aos fluxos de trabalho.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Software / AI Agents</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="A2" t="str">
+        <v>AGENT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Bruce - O Assistente Cognitivo Corporativo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Uma inteligência artificial desenhada para automatizar tarefas complexas, analisar dados financeiros e interagir com clientes em tempo real. Bruce aprende com o contexto da sua empresa e se adapta aos fluxos de trabalho.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Software / AI Agents</v>
+      </c>
+      <c r="E2">
         <v>25000</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>in_stock</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"features": ["Integra\u00e7\u00e3o RAG", "Vis\u00e3o Computacional", "An\u00e1lise de Sentimentos"], "target_audience": "Empresas B2B (M\u00e9dio e Grande Porte)", "implementation_time_weeks": 4}</t>
-        </is>
+      <c r="F2" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{"features":["Integração RAG","Visão Computacional","Análise de Sentimentos"],"target_audience":"Empresas B2B (Médio e Grande Porte)","implementation_time_weeks":4}</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AGENT-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Trillia Flow</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Plataforma de orquestração de APIs. Conecte dezenas de serviços sem escrever código. Ideal para operações de e-commerce e logística.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Software / SaaS</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="A3" t="str">
+        <v>AGENT-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Trillia Flow</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Plataforma de orquestração de APIs. Conecte dezenas de serviços sem escrever código. Ideal para operações de e-commerce e logística.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Software / SaaS</v>
+      </c>
+      <c r="E3">
         <v>5000</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>in_stock</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>{"features": ["Drag-and-Drop", "700+ Integra\u00e7\u00f5es", "Suporte 24/7"], "target_audience": "Startups e E-commerces", "implementation_time_weeks": 1}</t>
-        </is>
+      <c r="F3" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G3" t="str">
+        <v>{"features":["Drag-and-Drop","700+ Integrações","Suporte 24/7"],"target_audience":"Startups e E-commerces","implementation_time_weeks":1}</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CONSULT-100</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Consultoria de Implantação de Dados</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>50 horas de consultoria sênior para mapeamento de dados, criação de Data Lakes e estruturação de pipelines para receber inteligência artificial.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Serviços</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="A4" t="str">
+        <v>CONSULT-100</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Consultoria de Implantação de Dados</v>
+      </c>
+      <c r="C4" t="str">
+        <v>50 horas de consultoria sênior para mapeamento de dados, criação de Data Lakes e estruturação de pipelines para receber inteligência artificial.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Serviços</v>
+      </c>
+      <c r="E4">
         <v>18000</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>{"deliverables": ["Blueprint Arquitet\u00f4nico", "Pipeline ETL Customizado"], "professionals": ["Engenheiro de Dados", "Cientista de Dados"]}</t>
-        </is>
+      <c r="F4" t="str">
+        <v>available</v>
+      </c>
+      <c r="G4" t="str">
+        <v>{"deliverables":["Blueprint Arquitetônico","Pipeline ETL Customizado"],"professionals":["Engenheiro de Dados","Cientista de Dados"]}</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>MIH-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MARKET INTELLIGENCE HUB</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Plataforma centralizada de insights de mercado e análise competitiva em tempo real.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="F5" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G5" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H1","owner":"Ana Silva","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 5.000/mês","revenue":"R$ 1.2M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PRO-002</v>
+      </c>
+      <c r="B6" t="str">
+        <v>PROSPECTOR PRO</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ferramenta de geração e qualificação de leads B2B com enriquecimento de dados.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="F6" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G6" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H1","owner":"Bruno Costa","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 8.500/mês","revenue":"R$ 2.4M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>IDG-003</v>
+      </c>
+      <c r="B7" t="str">
+        <v>IDENTITY GUARD AI</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Sistema de verificação de identidade com biometria facial e análise documental.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="F7" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G7" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","owner":"Carlos Santos","squad":"Beta","mercado":"B2B","pricing":"Transacional - R$ 2,50/consulta","revenue":"R$ 4.8M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TSH-004</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TRANSACTIONAL SHIELD</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Motor de regras e IA para detecção de fraudes em transações financeiras em tempo real.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="F8" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G8" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","owner":"Daniela Lima","squad":"Beta","mercado":"B2B","pricing":"Transacional - 0.1% do volume processado","revenue":"R$ 7.2M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CDE-005</v>
+      </c>
+      <c r="B9" t="str">
+        <v>CREDIT DECISION ENGINE</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Motor de decisão automatizado para aprovação de crédito com modelos customizáveis.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="F9" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G9" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H1","owner":"Eduardo Rocha","squad":"Gamma","mercado":"B2B","pricing":"SaaS + Transacional","revenue":"R$ 3.1M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>REC-006</v>
+      </c>
+      <c r="B10" t="str">
+        <v>RECOVERY OPTIMIZER</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Plataforma de gestão e otimização de cobrança com canais digitais integrados.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="F10" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G10" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H1","owner":"Fernanda Oliveira","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 12.000/mês","revenue":"R$ 2.5M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SMU-007</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SMART UNDERWRITER</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Sistema de auxílio à subscrição de riscos complexos com análise de dados externos.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="F11" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G11" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H2","owner":"Gustavo Lima","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 15.000/mês","revenue":"R$ 0.8M ARR","horizonte":"H2"}</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>COL-008</v>
+      </c>
+      <c r="B12" t="str">
+        <v>COLLATERAL REGISTRY AI</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Plataforma para registro e avaliação automatizada de garantias reais.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="F12" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G12" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","owner":"Helena Souza","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 20.000/mês","revenue":"R$ 0.5M ARR","horizonte":"H2"}</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MDA-009</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MARKET DATA ANALYTICS HUB</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Terminal de análise de dados de mercado em tempo real para fundos e corretoras.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="F13" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G13" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","owner":"Igor Martins","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 4.000/usuário","revenue":"R$ 1.8M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>QUA-010</v>
+      </c>
+      <c r="B14" t="str">
+        <v>QUANTUM PREDICTOR</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Algoritmo quântico experimental para predição de cenários econômicos globais com alta precisão.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="F14" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G14" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H3","owner":"Helena Souza","squad":"Epsilon","mercado":"B2B","pricing":"Pesquisa e Desenvolvimento","revenue":"R$ 0 ARR","horizonte":"H3"}</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BLO-011</v>
+      </c>
+      <c r="B15" t="str">
+        <v>BLOCKCHAIN LEDGER</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Infraestrutura de registro distribuído para liquidação instantânea de ativos financeiros.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="F15" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G15" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","owner":"Igor Martins","squad":"Delta","mercado":"B2B","pricing":"SaaS + Taxa por transação","revenue":"R$ 0.3M ARR","horizonte":"H2"}</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CYB-012</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CYBER DEFENSE AI</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Sistema de defesa proativa contra ataques cibernéticos em infraestruturas críticas.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="F16" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G16" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","owner":"Carlos Santos","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 25.000/mês","revenue":"R$ 5.5M ARR","horizonte":"H1"}</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PROD-01</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Produto Mágico 1 - Loss Prevention</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Este é o Produto Mágico 1, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E17">
+        <v>1388</v>
+      </c>
+      <c r="F17" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G17" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 1","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 2549/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 1 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>PROD-02</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Produto Mágico 2 - Crédito e Cobrança</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Este é o Produto Mágico 2, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E18">
+        <v>1030</v>
+      </c>
+      <c r="F18" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G18" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 2","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 4839/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 2 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PROD-03</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Produto Mágico 3 - Cotação e Subscrição</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Este é o Produto Mágico 3, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E19">
+        <v>5597</v>
+      </c>
+      <c r="F19" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G19" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 3","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 512/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 3 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>PROD-04</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Produto Mágico 4 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Este é o Produto Mágico 4, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E20">
+        <v>6152</v>
+      </c>
+      <c r="F20" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G20" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 4","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 4445/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 4 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>PROD-05</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Produto Mágico 5 - Capital Markets</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Este é o Produto Mágico 5, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E21">
+        <v>2110</v>
+      </c>
+      <c r="F21" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G21" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 5","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 4735/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 5 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>PROD-06</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Produto Mágico 6 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Este é o Produto Mágico 6, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E22">
+        <v>9781</v>
+      </c>
+      <c r="F22" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G22" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 6","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 2851/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 6 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>PROD-07</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Produto Mágico 7 - Loss Prevention</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Este é o Produto Mágico 7, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E23">
+        <v>6821</v>
+      </c>
+      <c r="F23" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G23" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 7","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 4999/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 7 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>PROD-08</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Produto Mágico 8 - Crédito e Cobrança</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Este é o Produto Mágico 8, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E24">
+        <v>1337</v>
+      </c>
+      <c r="F24" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G24" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 8","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 5170/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 8 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PROD-09</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Produto Mágico 9 - Cotação e Subscrição</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Este é o Produto Mágico 9, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E25">
+        <v>6747</v>
+      </c>
+      <c r="F25" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G25" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 9","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 2261/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 9 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>PROD-010</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Produto Mágico 10 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Este é o Produto Mágico 10, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E26">
+        <v>6211</v>
+      </c>
+      <c r="F26" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G26" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 10","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 3531/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 10 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PROD-011</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Produto Mágico 11 - Capital Markets</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Este é o Produto Mágico 11, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E27">
+        <v>3125</v>
+      </c>
+      <c r="F27" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G27" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 11","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 5469/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 11 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PROD-012</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Produto Mágico 12 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Este é o Produto Mágico 12, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E28">
+        <v>5772</v>
+      </c>
+      <c r="F28" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G28" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 12","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 2805/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 12 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>PROD-013</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Produto Mágico 13 - Loss Prevention</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Este é o Produto Mágico 13, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E29">
+        <v>7993</v>
+      </c>
+      <c r="F29" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G29" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 13","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 2981/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 13 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>PROD-014</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Produto Mágico 14 - Crédito e Cobrança</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Este é o Produto Mágico 14, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E30">
+        <v>7809</v>
+      </c>
+      <c r="F30" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G30" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 14","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 651/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 14 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>PROD-015</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Produto Mágico 15 - Cotação e Subscrição</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Este é o Produto Mágico 15, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E31">
+        <v>1299</v>
+      </c>
+      <c r="F31" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G31" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 15","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 1622/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 15 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>PROD-016</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Produto Mágico 16 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Este é o Produto Mágico 16, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E32">
+        <v>6279</v>
+      </c>
+      <c r="F32" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G32" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 16","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 1918/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 16 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>PROD-017</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Produto Mágico 17 - Capital Markets</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Este é o Produto Mágico 17, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E33">
+        <v>7329</v>
+      </c>
+      <c r="F33" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G33" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 17","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 1069/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 17 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>PROD-018</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Produto Mágico 18 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Este é o Produto Mágico 18, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E34">
+        <v>7216</v>
+      </c>
+      <c r="F34" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G34" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 18","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 3082/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 18 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>PROD-019</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Produto Mágico 19 - Loss Prevention</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Este é o Produto Mágico 19, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E35">
+        <v>1585</v>
+      </c>
+      <c r="F35" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G35" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 19","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 4959/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 19 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>PROD-020</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Produto Mágico 20 - Crédito e Cobrança</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Este é o Produto Mágico 20, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E36">
+        <v>9905</v>
+      </c>
+      <c r="F36" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G36" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 20","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 5118/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 20 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>PROD-021</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Produto Mágico 21 - Cotação e Subscrição</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Este é o Produto Mágico 21, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E37">
+        <v>7347</v>
+      </c>
+      <c r="F37" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G37" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 21","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 3640/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 21 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>PROD-022</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Produto Mágico 22 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Este é o Produto Mágico 22, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E38">
+        <v>10958</v>
+      </c>
+      <c r="F38" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G38" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 22","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 2602/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 22 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>PROD-023</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Produto Mágico 23 - Capital Markets</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Este é o Produto Mágico 23, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E39">
+        <v>3932</v>
+      </c>
+      <c r="F39" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G39" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 23","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 3544/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 23 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>PROD-024</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Produto Mágico 24 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Este é o Produto Mágico 24, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E40">
+        <v>2530</v>
+      </c>
+      <c r="F40" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G40" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 24","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 3381/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 24 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>PROD-025</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Produto Mágico 25 - Loss Prevention</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Este é o Produto Mágico 25, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E41">
+        <v>1307</v>
+      </c>
+      <c r="F41" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G41" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 25","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 2485/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 25 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>PROD-026</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Produto Mágico 26 - Crédito e Cobrança</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Este é o Produto Mágico 26, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E42">
+        <v>4312</v>
+      </c>
+      <c r="F42" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G42" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 26","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 1902/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 26 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>PROD-027</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Produto Mágico 27 - Cotação e Subscrição</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Este é o Produto Mágico 27, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E43">
+        <v>3123</v>
+      </c>
+      <c r="F43" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G43" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 27","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 4895/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 27 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>PROD-028</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Produto Mágico 28 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Este é o Produto Mágico 28, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E44">
+        <v>9058</v>
+      </c>
+      <c r="F44" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G44" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 28","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 2697/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 28 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>PROD-029</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Produto Mágico 29 - Capital Markets</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Este é o Produto Mágico 29, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E45">
+        <v>1136</v>
+      </c>
+      <c r="F45" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G45" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 29","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 5128/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 29 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>PROD-030</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Produto Mágico 30 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Este é o Produto Mágico 30, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E46">
+        <v>9273</v>
+      </c>
+      <c r="F46" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G46" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 30","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 1526/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 30 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>PROD-031</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Produto Mágico 31 - Loss Prevention</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Este é o Produto Mágico 31, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E47">
+        <v>8348</v>
+      </c>
+      <c r="F47" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G47" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 31","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 1229/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 31 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>PROD-032</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Produto Mágico 32 - Crédito e Cobrança</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Este é o Produto Mágico 32, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E48">
+        <v>4693</v>
+      </c>
+      <c r="F48" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G48" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 32","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 5208/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 32 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>PROD-033</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Produto Mágico 33 - Cotação e Subscrição</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Este é o Produto Mágico 33, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E49">
+        <v>8015</v>
+      </c>
+      <c r="F49" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G49" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 33","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 4249/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 33 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>PROD-034</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Produto Mágico 34 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Este é o Produto Mágico 34, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E50">
+        <v>7860</v>
+      </c>
+      <c r="F50" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G50" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 34","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 2194/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 34 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>PROD-035</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Produto Mágico 35 - Capital Markets</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Este é o Produto Mágico 35, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E51">
+        <v>9264</v>
+      </c>
+      <c r="F51" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G51" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 35","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 1232/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 35 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>PROD-036</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Produto Mágico 36 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Este é o Produto Mágico 36, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D52" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E52">
+        <v>9388</v>
+      </c>
+      <c r="F52" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G52" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 36","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 2522/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 36 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>PROD-037</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Produto Mágico 37 - Loss Prevention</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Este é o Produto Mágico 37, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E53">
+        <v>5339</v>
+      </c>
+      <c r="F53" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G53" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 37","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 5373/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 37 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>PROD-038</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Produto Mágico 38 - Crédito e Cobrança</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Este é o Produto Mágico 38, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E54">
+        <v>7856</v>
+      </c>
+      <c r="F54" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G54" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 38","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 541/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 38 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>PROD-039</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Produto Mágico 39 - Cotação e Subscrição</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Este é o Produto Mágico 39, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E55">
+        <v>4369</v>
+      </c>
+      <c r="F55" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G55" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 39","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 1930/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 39 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>PROD-040</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Produto Mágico 40 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Este é o Produto Mágico 40, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E56">
+        <v>10178</v>
+      </c>
+      <c r="F56" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G56" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 40","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 2540/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 40 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>PROD-041</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Produto Mágico 41 - Capital Markets</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Este é o Produto Mágico 41, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E57">
+        <v>10527</v>
+      </c>
+      <c r="F57" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G57" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 41","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 2458/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 41 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>PROD-042</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Produto Mágico 42 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Este é o Produto Mágico 42, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D58" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E58">
+        <v>10856</v>
+      </c>
+      <c r="F58" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G58" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 42","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 1022/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 42 entra para automatizar isso completamente.","revenue":"R$ 3M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>PROD-043</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Produto Mágico 43 - Loss Prevention</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Este é o Produto Mágico 43, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E59">
+        <v>4703</v>
+      </c>
+      <c r="F59" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G59" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 43","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 5494/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 43 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>PROD-044</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Produto Mágico 44 - Crédito e Cobrança</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Este é o Produto Mágico 44, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E60">
+        <v>3333</v>
+      </c>
+      <c r="F60" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G60" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 44","squad":"Gamma","mercado":"B2B","pricing":"SaaS - R$ 1453/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 44 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>PROD-045</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Produto Mágico 45 - Cotação e Subscrição</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Este é o Produto Mágico 45, focado em resolver problemas críticos de Cotação e Subscrição. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E61">
+        <v>5090</v>
+      </c>
+      <c r="F61" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G61" t="str">
+        <v>{"bu":"Cotação e Subscrição","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 45","squad":"Delta","mercado":"B2B","pricing":"SaaS - R$ 3500/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Cotação e Subscrição. O Produto 45 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>PROD-046</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Produto Mágico 46 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Este é o Produto Mágico 46, focado em resolver problemas críticos de Negócios e Infraestrutura. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E62">
+        <v>8124</v>
+      </c>
+      <c r="F62" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G62" t="str">
+        <v>{"bu":"Negócios e Infraestrutura","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 46","squad":"Epsilon","mercado":"B2B","pricing":"SaaS - R$ 658/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Negócios e Infraestrutura. O Produto 46 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>PROD-047</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Produto Mágico 47 - Capital Markets</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Este é o Produto Mágico 47, focado em resolver problemas críticos de Capital Markets. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E63">
+        <v>3977</v>
+      </c>
+      <c r="F63" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G63" t="str">
+        <v>{"bu":"Capital Markets","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 47","squad":"Zeta","mercado":"B2B","pricing":"SaaS - R$ 3082/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Capital Markets. O Produto 47 entra para automatizar isso completamente.","revenue":"R$ 2M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>PROD-048</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Produto Mágico 48 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Este é o Produto Mágico 48, focado em resolver problemas críticos de S&amp;M e Inteligência de Mercado. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H3.</v>
+      </c>
+      <c r="D64" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E64">
+        <v>2262</v>
+      </c>
+      <c r="F64" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G64" t="str">
+        <v>{"bu":"S&amp;M e Inteligência de Mercado","tag":"H3","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 48","squad":"Eta","mercado":"B2B","pricing":"SaaS - R$ 2578/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de S&amp;M e Inteligência de Mercado. O Produto 48 entra para automatizar isso completamente.","revenue":"R$ 0M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H3","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>PROD-049</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Produto Mágico 49 - Loss Prevention</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Este é o Produto Mágico 49, focado em resolver problemas críticos de Loss Prevention. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H1.</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E65">
+        <v>3278</v>
+      </c>
+      <c r="F65" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G65" t="str">
+        <v>{"bu":"Loss Prevention","tag":"H1","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 49","squad":"Alpha","mercado":"B2B","pricing":"SaaS - R$ 4684/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Loss Prevention. O Produto 49 entra para automatizar isso completamente.","revenue":"R$ 1M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H1","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>PROD-050</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Produto Mágico 50 - Crédito e Cobrança</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Este é o Produto Mágico 50, focado em resolver problemas críticos de Crédito e Cobrança. Ele aumenta a eficiência em 30% e reduz custos operacionais. Ideal para clientes corporativos de grande porte que precisam escalar suas operações no horizonte H2.</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E66">
+        <v>7158</v>
+      </c>
+      <c r="F66" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="G66" t="str">
+        <v>{"bu":"Crédito e Cobrança","tag":"H2","tech":["TypeScript","Supabase","Gemini"],"owner":"Diretor 50","squad":"Beta","mercado":"B2B","pricing":"SaaS - R$ 1404/mês","problem":"As empresas atualmente perdem muito tempo com processos manuais na área de Crédito e Cobrança. O Produto 50 entra para automatizar isso completamente.","revenue":"R$ 4M ARR","useCases":["Automatização","Monitoramento Definitivo","Integrações robustas API"],"horizonte":"H2","solutions":["Arquitetura escalável","Machine Learning embarcado"]}</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G66"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1088,9 +1088,963 @@
         <v>C++, Python, Elastic Stack</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TRL-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>PRODUTO AVANÇADO 13 - Inovação e Pesquisa</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Solução robusta de nível enterprise para Inovação e Pesquisa, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="E14" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Eduardo Rocha</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Zeta</v>
+      </c>
+      <c r="H14" t="str">
+        <v>R$ 4M ARR</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="J14" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K14" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M14" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Inexistência de ferramentas escaláveis de Inovação e Pesquisa no mercado local.</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TRL-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PRODUTO AVANÇADO 14 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Solução robusta de nível enterprise para S&amp;M e Inteligência de Mercado, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E15" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Fernanda Oliveira</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Eta</v>
+      </c>
+      <c r="H15" t="str">
+        <v>R$ 4M ARR</v>
+      </c>
+      <c r="I15" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="J15" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K15" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M15" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Inexistência de ferramentas escaláveis de S&amp;M e Inteligência de Mercado no mercado local.</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TRL-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PRODUTO AVANÇADO 15 - Loss Prevention</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Solução robusta de nível enterprise para Loss Prevention, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E16" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Gustavo Lima</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Theta</v>
+      </c>
+      <c r="H16" t="str">
+        <v>R$ 1M ARR</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="J16" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K16" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L16" t="str">
+        <v>SaaS Premium</v>
+      </c>
+      <c r="M16" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N16" t="str">
+        <v>Inexistência de ferramentas escaláveis de Loss Prevention no mercado local.</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P16" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TRL-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>PRODUTO AVANÇADO 16 - Crédito e Cobrança</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Solução robusta de nível enterprise para Crédito e Cobrança, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E17" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Helena Souza</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Alpha</v>
+      </c>
+      <c r="H17" t="str">
+        <v>R$ 10M ARR</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="J17" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K17" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M17" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Inexistência de ferramentas escaláveis de Crédito e Cobrança no mercado local.</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P17" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TRL-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>PRODUTO AVANÇADO 17 - Cotação e Subscrição</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Solução robusta de nível enterprise para Cotação e Subscrição, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E18" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Igor Martins</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Beta</v>
+      </c>
+      <c r="H18" t="str">
+        <v>R$ 10M ARR</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="J18" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K18" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M18" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Inexistência de ferramentas escaláveis de Cotação e Subscrição no mercado local.</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P18" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TRL-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>PRODUTO AVANÇADO 18 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Solução robusta de nível enterprise para Negócios e Infraestrutura, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E19" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Daniela Lima</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Gamma</v>
+      </c>
+      <c r="H19" t="str">
+        <v>R$ 10M ARR</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="J19" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K19" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L19" t="str">
+        <v>SaaS Premium</v>
+      </c>
+      <c r="M19" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Inexistência de ferramentas escaláveis de Negócios e Infraestrutura no mercado local.</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P19" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TRL-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>PRODUTO AVANÇADO 19 - Capital Markets</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Solução robusta de nível enterprise para Capital Markets, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E20" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Carlos Santos</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Delta</v>
+      </c>
+      <c r="H20" t="str">
+        <v>R$ 5M ARR</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="J20" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K20" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M20" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Inexistência de ferramentas escaláveis de Capital Markets no mercado local.</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TRL-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>PRODUTO AVANÇADO 20 - Inovação e Pesquisa</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Solução robusta de nível enterprise para Inovação e Pesquisa, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="E21" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Ana Silva</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Epsilon</v>
+      </c>
+      <c r="H21" t="str">
+        <v>R$ 3M ARR</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="J21" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K21" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M21" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Inexistência de ferramentas escaláveis de Inovação e Pesquisa no mercado local.</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TRL-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>PRODUTO AVANÇADO 21 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Solução robusta de nível enterprise para S&amp;M e Inteligência de Mercado, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E22" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Bruno Costa</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Zeta</v>
+      </c>
+      <c r="H22" t="str">
+        <v>R$ 9M ARR</v>
+      </c>
+      <c r="I22" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="J22" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K22" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L22" t="str">
+        <v>SaaS Premium</v>
+      </c>
+      <c r="M22" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Inexistência de ferramentas escaláveis de S&amp;M e Inteligência de Mercado no mercado local.</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P22" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TRL-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>PRODUTO AVANÇADO 22 - Loss Prevention</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Solução robusta de nível enterprise para Loss Prevention, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E23" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Eduardo Rocha</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Eta</v>
+      </c>
+      <c r="H23" t="str">
+        <v>R$ 5M ARR</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="J23" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K23" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M23" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Inexistência de ferramentas escaláveis de Loss Prevention no mercado local.</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P23" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TRL-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>PRODUTO AVANÇADO 23 - Crédito e Cobrança</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Solução robusta de nível enterprise para Crédito e Cobrança, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E24" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Fernanda Oliveira</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Theta</v>
+      </c>
+      <c r="H24" t="str">
+        <v>R$ 6M ARR</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="J24" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K24" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M24" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Inexistência de ferramentas escaláveis de Crédito e Cobrança no mercado local.</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P24" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TRL-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PRODUTO AVANÇADO 24 - Cotação e Subscrição</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Solução robusta de nível enterprise para Cotação e Subscrição, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E25" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Gustavo Lima</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Alpha</v>
+      </c>
+      <c r="H25" t="str">
+        <v>R$ 4M ARR</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="J25" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K25" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L25" t="str">
+        <v>SaaS Premium</v>
+      </c>
+      <c r="M25" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Inexistência de ferramentas escaláveis de Cotação e Subscrição no mercado local.</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P25" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TRL-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>PRODUTO AVANÇADO 25 - Negócios e Infraestrutura</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Solução robusta de nível enterprise para Negócios e Infraestrutura, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E26" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Helena Souza</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Beta</v>
+      </c>
+      <c r="H26" t="str">
+        <v>R$ 8M ARR</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="J26" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K26" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M26" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Inexistência de ferramentas escaláveis de Negócios e Infraestrutura no mercado local.</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P26" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TRL-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>PRODUTO AVANÇADO 26 - Capital Markets</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Solução robusta de nível enterprise para Capital Markets, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E27" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Igor Martins</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Gamma</v>
+      </c>
+      <c r="H27" t="str">
+        <v>R$ 3M ARR</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="J27" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K27" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M27" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Inexistência de ferramentas escaláveis de Capital Markets no mercado local.</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P27" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TRL-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>PRODUTO AVANÇADO 27 - Inovação e Pesquisa</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Solução robusta de nível enterprise para Inovação e Pesquisa, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="E28" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Daniela Lima</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Delta</v>
+      </c>
+      <c r="H28" t="str">
+        <v>R$ 7M ARR</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="J28" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K28" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L28" t="str">
+        <v>SaaS Premium</v>
+      </c>
+      <c r="M28" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Inexistência de ferramentas escaláveis de Inovação e Pesquisa no mercado local.</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P28" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TRL-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>PRODUTO AVANÇADO 28 - S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Solução robusta de nível enterprise para S&amp;M e Inteligência de Mercado, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E29" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Carlos Santos</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Epsilon</v>
+      </c>
+      <c r="H29" t="str">
+        <v>R$ 3M ARR</v>
+      </c>
+      <c r="I29" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="J29" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K29" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M29" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Inexistência de ferramentas escaláveis de S&amp;M e Inteligência de Mercado no mercado local.</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P29" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TRL-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>PRODUTO AVANÇADO 29 - Loss Prevention</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Solução robusta de nível enterprise para Loss Prevention, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="E30" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Ana Silva</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Zeta</v>
+      </c>
+      <c r="H30" t="str">
+        <v>R$ 8M ARR</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Loss Prevention</v>
+      </c>
+      <c r="J30" t="str">
+        <v>PME</v>
+      </c>
+      <c r="K30" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Licença Corporativa</v>
+      </c>
+      <c r="M30" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Inexistência de ferramentas escaláveis de Loss Prevention no mercado local.</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P30" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TRL-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>PRODUTO AVANÇADO 30 - Crédito e Cobrança</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Solução robusta de nível enterprise para Crédito e Cobrança, otimizada para o ecossistema Trillia.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="E31" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Bruno Costa</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Eta</v>
+      </c>
+      <c r="H31" t="str">
+        <v>R$ 5M ARR</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Crédito e Cobrança</v>
+      </c>
+      <c r="J31" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K31" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L31" t="str">
+        <v>SaaS Premium</v>
+      </c>
+      <c r="M31" t="str">
+        <v>https://trillia.com.br</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Inexistência de ferramentas escaláveis de Crédito e Cobrança no mercado local.</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Automação de workflows, Business intelligence, Segurança de dados</v>
+      </c>
+      <c r="P31" t="str">
+        <v>Microsserviços auto-escaláveis, Lakehouse integration, AI-first architecture</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:R36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,6 +451,9 @@
       <c r="Q1" t="str">
         <v>tech_stack</v>
       </c>
+      <c r="R1" t="str">
+        <v>owner_email</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -472,7 +475,7 @@
         <v>Ana Silva</v>
       </c>
       <c r="G2" t="str">
-        <v>Alpha</v>
+        <v>SQUAD ALPHA PRIME</v>
       </c>
       <c r="H2" t="str">
         <v>R$ 1.2M ARR</v>
@@ -503,6 +506,9 @@
       </c>
       <c r="Q2" t="str">
         <v>Python, Spark, Power BI, Azure</v>
+      </c>
+      <c r="R2" t="str">
+        <v>ana.silva@trillia.com.br</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +531,7 @@
         <v>Bruno Costa</v>
       </c>
       <c r="G3" t="str">
-        <v>Alpha</v>
+        <v>SQUAD ALPHA PRIME</v>
       </c>
       <c r="H3" t="str">
         <v>R$ 2.4M ARR</v>
@@ -556,6 +562,9 @@
       </c>
       <c r="Q3" t="str">
         <v>Node.js, MongoDB, React</v>
+      </c>
+      <c r="R3" t="str">
+        <v>bruno.costa@trillia.com.br</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +587,7 @@
         <v>Carlos Santos</v>
       </c>
       <c r="G4" t="str">
-        <v>Beta</v>
+        <v>SQUAD BETA NEXUS</v>
       </c>
       <c r="H4" t="str">
         <v>R$ 4.8M ARR</v>
@@ -609,6 +618,9 @@
       </c>
       <c r="Q4" t="str">
         <v>Python, TensorFlow, AWS Rekognition</v>
+      </c>
+      <c r="R4" t="str">
+        <v>carlos.santos@trillia.com.br</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +643,7 @@
         <v>Daniela Lima</v>
       </c>
       <c r="G5" t="str">
-        <v>Beta</v>
+        <v>SQUAD BETA NEXUS</v>
       </c>
       <c r="H5" t="str">
         <v>R$ 7.2M ARR</v>
@@ -662,6 +674,9 @@
       </c>
       <c r="Q5" t="str">
         <v>Go, Redis, Kubernetes</v>
+      </c>
+      <c r="R5" t="str">
+        <v>daniela.lima@trillia.com.br</v>
       </c>
     </row>
     <row r="6">
@@ -684,7 +699,7 @@
         <v>Eduardo Rocha</v>
       </c>
       <c r="G6" t="str">
-        <v>Gamma</v>
+        <v>SQUAD GAMMA CORE</v>
       </c>
       <c r="H6" t="str">
         <v>R$ 3.1M ARR</v>
@@ -715,6 +730,9 @@
       </c>
       <c r="Q6" t="str">
         <v>Java, Spring Boot, PostgreSQL</v>
+      </c>
+      <c r="R6" t="str">
+        <v>eduardo.rocha@trillia.com.br</v>
       </c>
     </row>
     <row r="7">
@@ -737,7 +755,7 @@
         <v>Fernanda Oliveira</v>
       </c>
       <c r="G7" t="str">
-        <v>Gamma</v>
+        <v>SQUAD GAMMA CORE</v>
       </c>
       <c r="H7" t="str">
         <v>R$ 2.5M ARR</v>
@@ -768,6 +786,9 @@
       </c>
       <c r="Q7" t="str">
         <v>PHP (Laravel), MySQL, Twilio</v>
+      </c>
+      <c r="R7" t="str">
+        <v>fernanda.oliveira@trillia.com.br</v>
       </c>
     </row>
     <row r="8">
@@ -790,7 +811,7 @@
         <v>Gustavo Lima</v>
       </c>
       <c r="G8" t="str">
-        <v>Delta</v>
+        <v>SQUAD DELTA FORCE</v>
       </c>
       <c r="H8" t="str">
         <v>R$ 0.8M ARR</v>
@@ -821,6 +842,9 @@
       </c>
       <c r="Q8" t="str">
         <v>C#, .NET Core, SQL Server</v>
+      </c>
+      <c r="R8" t="str">
+        <v>gustavo.lima@trillia.com.br</v>
       </c>
     </row>
     <row r="9">
@@ -843,7 +867,7 @@
         <v>Helena Souza</v>
       </c>
       <c r="G9" t="str">
-        <v>Delta</v>
+        <v>SQUAD DELTA FORCE</v>
       </c>
       <c r="H9" t="str">
         <v>R$ 0.5M ARR</v>
@@ -874,6 +898,9 @@
       </c>
       <c r="Q9" t="str">
         <v>Python, Django, Hyperledger</v>
+      </c>
+      <c r="R9" t="str">
+        <v>helena.souza@trillia.com.br</v>
       </c>
     </row>
     <row r="10">
@@ -896,7 +923,7 @@
         <v>Igor Martins</v>
       </c>
       <c r="G10" t="str">
-        <v>Epsilon</v>
+        <v>SQUAD EPSILON STRAT</v>
       </c>
       <c r="H10" t="str">
         <v>R$ 1.8M ARR</v>
@@ -927,6 +954,9 @@
       </c>
       <c r="Q10" t="str">
         <v>Rust, WebAssembly, ClickHouse</v>
+      </c>
+      <c r="R10" t="str">
+        <v>igor.martins@trillia.com.br</v>
       </c>
     </row>
     <row r="11">
@@ -949,7 +979,7 @@
         <v>Helena Souza</v>
       </c>
       <c r="G11" t="str">
-        <v>Epsilon</v>
+        <v>SQUAD EPSILON STRAT</v>
       </c>
       <c r="H11" t="str">
         <v>R$ 0 ARR</v>
@@ -980,6 +1010,9 @@
       </c>
       <c r="Q11" t="str">
         <v>Q#, Python, Azure Quantum</v>
+      </c>
+      <c r="R11" t="str">
+        <v>helena.souza@trillia.com.br</v>
       </c>
     </row>
     <row r="12">
@@ -1002,7 +1035,7 @@
         <v>Igor Martins</v>
       </c>
       <c r="G12" t="str">
-        <v>Delta</v>
+        <v>SQUAD DELTA FORCE</v>
       </c>
       <c r="H12" t="str">
         <v>R$ 0.3M ARR</v>
@@ -1033,6 +1066,9 @@
       </c>
       <c r="Q12" t="str">
         <v>Solidity, Ethereum, Infura</v>
+      </c>
+      <c r="R12" t="str">
+        <v>igor.martins@trillia.com.br</v>
       </c>
     </row>
     <row r="13">
@@ -1055,7 +1091,7 @@
         <v>Carlos Santos</v>
       </c>
       <c r="G13" t="str">
-        <v>Beta</v>
+        <v>SQUAD BETA NEXUS</v>
       </c>
       <c r="H13" t="str">
         <v>R$ 5.5M ARR</v>
@@ -1086,6 +1122,9 @@
       </c>
       <c r="Q13" t="str">
         <v>C++, Python, Elastic Stack</v>
+      </c>
+      <c r="R13" t="str">
+        <v>carlos.santos@trillia.com.br</v>
       </c>
     </row>
     <row r="14">
@@ -1108,7 +1147,7 @@
         <v>Eduardo Rocha</v>
       </c>
       <c r="G14" t="str">
-        <v>Zeta</v>
+        <v>SQUAD ZETA VISION</v>
       </c>
       <c r="H14" t="str">
         <v>R$ 4M ARR</v>
@@ -1139,6 +1178,9 @@
       </c>
       <c r="Q14" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R14" t="str">
+        <v>eduardo.rocha@trillia.com.br</v>
       </c>
     </row>
     <row r="15">
@@ -1161,7 +1203,7 @@
         <v>Fernanda Oliveira</v>
       </c>
       <c r="G15" t="str">
-        <v>Eta</v>
+        <v>SQUAD ETA SOLUTIONS</v>
       </c>
       <c r="H15" t="str">
         <v>R$ 4M ARR</v>
@@ -1192,6 +1234,9 @@
       </c>
       <c r="Q15" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R15" t="str">
+        <v>fernanda.oliveira@trillia.com.br</v>
       </c>
     </row>
     <row r="16">
@@ -1214,7 +1259,7 @@
         <v>Gustavo Lima</v>
       </c>
       <c r="G16" t="str">
-        <v>Theta</v>
+        <v>SQUAD THETA LABS</v>
       </c>
       <c r="H16" t="str">
         <v>R$ 1M ARR</v>
@@ -1245,6 +1290,9 @@
       </c>
       <c r="Q16" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R16" t="str">
+        <v>gustavo.lima@trillia.com.br</v>
       </c>
     </row>
     <row r="17">
@@ -1267,7 +1315,7 @@
         <v>Helena Souza</v>
       </c>
       <c r="G17" t="str">
-        <v>Alpha</v>
+        <v>SQUAD ALPHA PRIME</v>
       </c>
       <c r="H17" t="str">
         <v>R$ 10M ARR</v>
@@ -1298,6 +1346,9 @@
       </c>
       <c r="Q17" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R17" t="str">
+        <v>helena.souza@trillia.com.br</v>
       </c>
     </row>
     <row r="18">
@@ -1320,7 +1371,7 @@
         <v>Igor Martins</v>
       </c>
       <c r="G18" t="str">
-        <v>Beta</v>
+        <v>SQUAD BETA NEXUS</v>
       </c>
       <c r="H18" t="str">
         <v>R$ 10M ARR</v>
@@ -1351,6 +1402,9 @@
       </c>
       <c r="Q18" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R18" t="str">
+        <v>igor.martins@trillia.com.br</v>
       </c>
     </row>
     <row r="19">
@@ -1373,7 +1427,7 @@
         <v>Daniela Lima</v>
       </c>
       <c r="G19" t="str">
-        <v>Gamma</v>
+        <v>SQUAD GAMMA CORE</v>
       </c>
       <c r="H19" t="str">
         <v>R$ 10M ARR</v>
@@ -1404,6 +1458,9 @@
       </c>
       <c r="Q19" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R19" t="str">
+        <v>daniela.lima@trillia.com.br</v>
       </c>
     </row>
     <row r="20">
@@ -1426,7 +1483,7 @@
         <v>Carlos Santos</v>
       </c>
       <c r="G20" t="str">
-        <v>Delta</v>
+        <v>SQUAD DELTA FORCE</v>
       </c>
       <c r="H20" t="str">
         <v>R$ 5M ARR</v>
@@ -1457,6 +1514,9 @@
       </c>
       <c r="Q20" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R20" t="str">
+        <v>carlos.santos@trillia.com.br</v>
       </c>
     </row>
     <row r="21">
@@ -1479,7 +1539,7 @@
         <v>Ana Silva</v>
       </c>
       <c r="G21" t="str">
-        <v>Epsilon</v>
+        <v>SQUAD EPSILON STRAT</v>
       </c>
       <c r="H21" t="str">
         <v>R$ 3M ARR</v>
@@ -1510,6 +1570,9 @@
       </c>
       <c r="Q21" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R21" t="str">
+        <v>ana.silva@trillia.com.br</v>
       </c>
     </row>
     <row r="22">
@@ -1532,7 +1595,7 @@
         <v>Bruno Costa</v>
       </c>
       <c r="G22" t="str">
-        <v>Zeta</v>
+        <v>SQUAD ZETA VISION</v>
       </c>
       <c r="H22" t="str">
         <v>R$ 9M ARR</v>
@@ -1563,6 +1626,9 @@
       </c>
       <c r="Q22" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R22" t="str">
+        <v>bruno.costa@trillia.com.br</v>
       </c>
     </row>
     <row r="23">
@@ -1585,7 +1651,7 @@
         <v>Eduardo Rocha</v>
       </c>
       <c r="G23" t="str">
-        <v>Eta</v>
+        <v>SQUAD ETA SOLUTIONS</v>
       </c>
       <c r="H23" t="str">
         <v>R$ 5M ARR</v>
@@ -1616,6 +1682,9 @@
       </c>
       <c r="Q23" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R23" t="str">
+        <v>eduardo.rocha@trillia.com.br</v>
       </c>
     </row>
     <row r="24">
@@ -1638,7 +1707,7 @@
         <v>Fernanda Oliveira</v>
       </c>
       <c r="G24" t="str">
-        <v>Theta</v>
+        <v>SQUAD THETA LABS</v>
       </c>
       <c r="H24" t="str">
         <v>R$ 6M ARR</v>
@@ -1669,6 +1738,9 @@
       </c>
       <c r="Q24" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R24" t="str">
+        <v>fernanda.oliveira@trillia.com.br</v>
       </c>
     </row>
     <row r="25">
@@ -1691,7 +1763,7 @@
         <v>Gustavo Lima</v>
       </c>
       <c r="G25" t="str">
-        <v>Alpha</v>
+        <v>SQUAD ALPHA PRIME</v>
       </c>
       <c r="H25" t="str">
         <v>R$ 4M ARR</v>
@@ -1722,6 +1794,9 @@
       </c>
       <c r="Q25" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R25" t="str">
+        <v>gustavo.lima@trillia.com.br</v>
       </c>
     </row>
     <row r="26">
@@ -1744,7 +1819,7 @@
         <v>Helena Souza</v>
       </c>
       <c r="G26" t="str">
-        <v>Beta</v>
+        <v>SQUAD BETA NEXUS</v>
       </c>
       <c r="H26" t="str">
         <v>R$ 8M ARR</v>
@@ -1775,6 +1850,9 @@
       </c>
       <c r="Q26" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R26" t="str">
+        <v>helena.souza@trillia.com.br</v>
       </c>
     </row>
     <row r="27">
@@ -1797,7 +1875,7 @@
         <v>Igor Martins</v>
       </c>
       <c r="G27" t="str">
-        <v>Gamma</v>
+        <v>SQUAD GAMMA CORE</v>
       </c>
       <c r="H27" t="str">
         <v>R$ 3M ARR</v>
@@ -1828,6 +1906,9 @@
       </c>
       <c r="Q27" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R27" t="str">
+        <v>igor.martins@trillia.com.br</v>
       </c>
     </row>
     <row r="28">
@@ -1850,7 +1931,7 @@
         <v>Daniela Lima</v>
       </c>
       <c r="G28" t="str">
-        <v>Delta</v>
+        <v>SQUAD DELTA FORCE</v>
       </c>
       <c r="H28" t="str">
         <v>R$ 7M ARR</v>
@@ -1881,6 +1962,9 @@
       </c>
       <c r="Q28" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R28" t="str">
+        <v>daniela.lima@trillia.com.br</v>
       </c>
     </row>
     <row r="29">
@@ -1903,7 +1987,7 @@
         <v>Carlos Santos</v>
       </c>
       <c r="G29" t="str">
-        <v>Epsilon</v>
+        <v>SQUAD EPSILON STRAT</v>
       </c>
       <c r="H29" t="str">
         <v>R$ 3M ARR</v>
@@ -1934,6 +2018,9 @@
       </c>
       <c r="Q29" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R29" t="str">
+        <v>carlos.santos@trillia.com.br</v>
       </c>
     </row>
     <row r="30">
@@ -1956,7 +2043,7 @@
         <v>Ana Silva</v>
       </c>
       <c r="G30" t="str">
-        <v>Zeta</v>
+        <v>SQUAD ZETA VISION</v>
       </c>
       <c r="H30" t="str">
         <v>R$ 8M ARR</v>
@@ -1987,6 +2074,9 @@
       </c>
       <c r="Q30" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
+      </c>
+      <c r="R30" t="str">
+        <v>ana.silva@trillia.com.br</v>
       </c>
     </row>
     <row r="31">
@@ -2009,7 +2099,7 @@
         <v>Bruno Costa</v>
       </c>
       <c r="G31" t="str">
-        <v>Eta</v>
+        <v>SQUAD ETA SOLUTIONS</v>
       </c>
       <c r="H31" t="str">
         <v>R$ 5M ARR</v>
@@ -2041,10 +2131,293 @@
       <c r="Q31" t="str">
         <v>TypeScript, Docker, AWS, Snowflake</v>
       </c>
+      <c r="R31" t="str">
+        <v>bruno.costa@trillia.com.br</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TRL-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>REAL-TIME LIQUIDITY MONITOR</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Monitoramento contínuo de liquidez para ativos de Capital Markets.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="E32" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Fernanda Oliveira</v>
+      </c>
+      <c r="G32" t="str">
+        <v>SQUAD DELTA FORCE</v>
+      </c>
+      <c r="H32" t="str">
+        <v>R$ 800k ARR</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Capital Markets</v>
+      </c>
+      <c r="J32" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K32" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Mensal</v>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v>Gargalos de liquidez não detectados.</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Monitoramento, Alertas, Dashboard</v>
+      </c>
+      <c r="P32" t="str">
+        <v>Streaming de Dados, In-memory DB</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>C#, Kafka, Redis</v>
+      </c>
+      <c r="R32" t="str">
+        <v>fernanda.oliveira@trillia.com.br</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TRL-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ESG SCORING ENGINE</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Motor de score baseado em critérios ESG para portfólios de investimento.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="E33" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Gabriel Silva</v>
+      </c>
+      <c r="G33" t="str">
+        <v>SQUAD DEEP DIVE AI</v>
+      </c>
+      <c r="H33" t="str">
+        <v>R$ 500k ARR</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Inovação e Pesquisa</v>
+      </c>
+      <c r="J33" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K33" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Anual</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v>Dificuldade em quantificar impacto ESG.</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Rating, Compliance, Relatórios</v>
+      </c>
+      <c r="P33" t="str">
+        <v>NLP para relatórios, Modelos Estatísticos</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>Python, PyTorch, MongoDB</v>
+      </c>
+      <c r="R33" t="str">
+        <v>gabriel.silva@trillia.com.br</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TRL-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>PREDICTIVE CHURN AI</v>
+      </c>
+      <c r="C34" t="str">
+        <v>IA para predizer cancelamentos de clientes em tempo real.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="E34" t="str">
+        <v>H1</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Ana Silva</v>
+      </c>
+      <c r="G34" t="str">
+        <v>SQUAD ALPHA PRIME</v>
+      </c>
+      <c r="H34" t="str">
+        <v>R$ 1.5M ARR</v>
+      </c>
+      <c r="I34" t="str">
+        <v>S&amp;M e Inteligência de Mercado</v>
+      </c>
+      <c r="J34" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K34" t="str">
+        <v>H1</v>
+      </c>
+      <c r="L34" t="str">
+        <v>SaaS</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v>Alta taxa de cancelamento sem aviso prévio.</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Retenção, Scoring de Churn</v>
+      </c>
+      <c r="P34" t="str">
+        <v>Random Forests, XGBoost</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Python, Scikit-learn, Snowflake</v>
+      </c>
+      <c r="R34" t="str">
+        <v>ana.silva@trillia.com.br</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TRL-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>AUTO-SETTLEMENT NODE</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Liquidação automática de ativos via redes distribuídas.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="E35" t="str">
+        <v>H3</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Lucas Mendes</v>
+      </c>
+      <c r="G35" t="str">
+        <v>SQUAD QUANTUM COMPUTING</v>
+      </c>
+      <c r="H35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Negócios e Infraestrutura</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Web3</v>
+      </c>
+      <c r="K35" t="str">
+        <v>H3</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Transacional</v>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v>Lentidão em processos de liquidez tradicionais.</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Settlement, Trustless Transactions</v>
+      </c>
+      <c r="P35" t="str">
+        <v>Smart Contracts, Blockchain Layer 2</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>Solidity, Rust, Ethereum</v>
+      </c>
+      <c r="R35" t="str">
+        <v>lucas.mendes@trillia.com.br</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TRL-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>DYNAMIC PRICING BOT</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Ajuste automático de preços para cotações complexas.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="E36" t="str">
+        <v>H2</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Roberto Mendes</v>
+      </c>
+      <c r="G36" t="str">
+        <v>SQUAD GAMMA CORE</v>
+      </c>
+      <c r="H36" t="str">
+        <v>R$ 1.2M ARR</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Cotação e Subscrição</v>
+      </c>
+      <c r="J36" t="str">
+        <v>B2B</v>
+      </c>
+      <c r="K36" t="str">
+        <v>H2</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Percentual de Margem</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v>Margens baixas por precificação estática.</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Otimização de Preço, Cotação Automática</v>
+      </c>
+      <c r="P36" t="str">
+        <v>Algoritmos Genéticos, Simulação Monte Carlo</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>Node.js, C++</v>
+      </c>
+      <c r="R36" t="str">
+        <v>roberto.mendes@trillia.com.br</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R36"/>
   </ignoredErrors>
 </worksheet>
 </file>